--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486398_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486398_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. KALSCHEUR</t>
+          <t>R. DIAS MARQUES LISBOA SANTOS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3081</v>
+        <v>3.7515</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5086</v>
+        <v>5.2189</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.2005</v>
+        <v>-1.4673</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7159</v>
+        <v>2.3404</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.8492</v>
+        <v>2.9715</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5652</v>
+        <v>-0.6311</v>
       </c>
       <c r="J2" t="n">
-        <v>4.949</v>
+        <v>4.2411</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1214</v>
+        <v>3.8538</v>
       </c>
       <c r="L2" t="n">
-        <v>5.0705</v>
+        <v>0.3873</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.2331</v>
+        <v>-1.9007</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.7278</v>
+        <v>-0.8823</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.5053</v>
+        <v>-1.0184</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.3926</v>
+        <v>-1.305</v>
       </c>
       <c r="R2" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8102</v>
+        <v>0.1289</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6922</v>
+        <v>0.0228</v>
       </c>
       <c r="U2" t="n">
-        <v>0.118</v>
+        <v>0.106</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8695</v>
+        <v>1.4997</v>
       </c>
       <c r="W2" t="n">
         <v>2.2599</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3904</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. DIAS MARQUES LISBOA SANTOS</t>
+          <t>G. KALSCHEUR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6482</v>
+        <v>3.7032</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4546</v>
+        <v>5.5338</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8064</v>
+        <v>-1.8306</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3404</v>
+        <v>1.7159</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9715</v>
+        <v>-1.8492</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6311</v>
+        <v>3.5652</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2411</v>
+        <v>4.949</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8538</v>
+        <v>-0.1214</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3873</v>
+        <v>5.0705</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9007</v>
+        <v>-3.2331</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8823</v>
+        <v>-1.7278</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0184</v>
+        <v>-1.5053</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.305</v>
+        <v>-2.3926</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9745</v>
+        <v>1.2053</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7413999999999999</v>
+        <v>0.7174</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.233</v>
+        <v>0.4879</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4997</v>
+        <v>1.8695</v>
       </c>
       <c r="W3" t="n">
         <v>2.2599</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.7602</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. SARAIVA SEIXAS</t>
+          <t>I. VAZQUEZ PEREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3112</v>
+        <v>2.853</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5951</v>
+        <v>4.493</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2839</v>
+        <v>-1.64</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7118</v>
+        <v>2.293</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2766</v>
+        <v>0.9399</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4352</v>
+        <v>1.3531</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9135</v>
+        <v>4.6606</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6935</v>
+        <v>2.2693</v>
       </c>
       <c r="L4" t="n">
-        <v>2.2201</v>
+        <v>2.3914</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2018</v>
+        <v>-2.3677</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4169</v>
+        <v>-1.3293</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7849</v>
+        <v>-1.0383</v>
       </c>
       <c r="P4" t="n">
-        <v>0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1644</v>
+        <v>0.7775</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3184</v>
+        <v>0.7246</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4828</v>
+        <v>0.0529</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ PEREZ</t>
+          <t>D. SARAIVA SEIXAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2141</v>
+        <v>2.6533</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9774</v>
+        <v>2.9989</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7633</v>
+        <v>-0.3456</v>
       </c>
       <c r="G5" t="n">
-        <v>2.293</v>
+        <v>1.7118</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9399</v>
+        <v>0.2766</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3531</v>
+        <v>1.4352</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6606</v>
+        <v>2.9135</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2693</v>
+        <v>0.6935</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3914</v>
+        <v>2.2201</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3677</v>
+        <v>-1.2018</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3293</v>
+        <v>-0.4169</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0383</v>
+        <v>-0.7849</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1387</v>
+        <v>0.5065</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2091</v>
+        <v>0.0853</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0704</v>
+        <v>0.4212</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0875</v>
+        <v>2.025</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7178</v>
+        <v>1.5628</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3698</v>
+        <v>0.4622</v>
       </c>
       <c r="G6" t="n">
         <v>1.5104</v>
@@ -922,13 +922,13 @@
         <v>0.2175</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3597</v>
+        <v>0.2971</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4026</v>
+        <v>0.2476</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0429</v>
+        <v>0.0496</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0811</v>
+        <v>0.9715</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1651</v>
+        <v>0.3021</v>
       </c>
       <c r="F7" t="n">
-        <v>0.916</v>
+        <v>0.6694</v>
       </c>
       <c r="G7" t="n">
         <v>1.3518</v>
@@ -1000,13 +1000,13 @@
         <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3595</v>
+        <v>0.2499</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1286</v>
+        <v>0.2656</v>
       </c>
       <c r="U7" t="n">
-        <v>0.231</v>
+        <v>-0.0156</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1952</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4492</v>
+        <v>-0.6046</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3711</v>
+        <v>-0.0539</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0781</v>
+        <v>-0.5508</v>
       </c>
       <c r="G8" t="n">
         <v>1.0076</v>
@@ -1078,13 +1078,13 @@
         <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2381</v>
+        <v>1.0827</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1286</v>
+        <v>0.4458</v>
       </c>
       <c r="U8" t="n">
-        <v>1.1095</v>
+        <v>0.6369</v>
       </c>
       <c r="V8" t="n">
         <v>-2.2599</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. OKANU</t>
+          <t>S. MC DONNELL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1698</v>
+        <v>-1.7643</v>
       </c>
       <c r="E9" t="n">
-        <v>0.047</v>
+        <v>2.3829</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2168</v>
+        <v>-4.1472</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.0738</v>
+        <v>-1.2129</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0004</v>
+        <v>-0.879</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0734</v>
+        <v>-0.3339</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7731</v>
+        <v>2.0202</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3341</v>
+        <v>0.6998</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4391</v>
+        <v>1.3204</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3007</v>
+        <v>-3.2331</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6663</v>
+        <v>-1.5788</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6344</v>
+        <v>-1.6543</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.3926</v>
+        <v>1.0875</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6017</v>
+        <v>0.7955</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3878</v>
+        <v>0.5372</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2139</v>
+        <v>0.2584</v>
       </c>
       <c r="V9" t="n">
-        <v>1.695</v>
+        <v>-2.4345</v>
       </c>
       <c r="W9" t="n">
-        <v>1.695</v>
+        <v>-0.1745</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. MC DONNELL</t>
+          <t>C. OKANU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6093</v>
+        <v>-2.7344</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5379</v>
+        <v>-1.5176</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.1472</v>
+        <v>-1.2168</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2129</v>
+        <v>-3.0738</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.879</v>
+        <v>-1.0004</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3339</v>
+        <v>-2.0734</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0202</v>
+        <v>-0.7731</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6998</v>
+        <v>-0.3341</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3204</v>
+        <v>-0.4391</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.2331</v>
+        <v>-2.3007</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5788</v>
+        <v>-0.6663</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6543</v>
+        <v>-1.6344</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0875</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9505</v>
+        <v>1.0371</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6922</v>
+        <v>0.8232</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2584</v>
+        <v>0.2139</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.4345</v>
+        <v>1.695</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1745</v>
+        <v>1.695</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.4071</v>
+        <v>-8.7606</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.9532</v>
+        <v>-6.2142</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4539</v>
+        <v>-2.5464</v>
       </c>
       <c r="G11" t="n">
         <v>-5.0544</v>
@@ -1312,13 +1312,13 @@
         <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6132</v>
+        <v>0.0333</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.0541</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0717</v>
+        <v>-0.0207</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4345</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.014800000000001</v>
+        <v>2.093599999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>13.6792</v>
+        <v>14.7067</v>
       </c>
       <c r="F12" t="n">
-        <v>-12.6643</v>
+        <v>-12.6131</v>
       </c>
       <c r="G12" t="n">
         <v>2.589799999999999</v>
@@ -1381,7 +1381,7 @@
         <v>-6.4587</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.3501</v>
+        <v>-4.350099999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-13.0503</v>
@@ -1390,16 +1390,16 @@
         <v>8.699999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>5.0351</v>
+        <v>6.113799999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8963</v>
+        <v>3.9236</v>
       </c>
       <c r="U12" t="n">
-        <v>2.139</v>
+        <v>2.1905</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.2599</v>
+        <v>-2.259899999999999</v>
       </c>
       <c r="W12" t="n">
         <v>5.886399999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.8491</v>
+        <v>5.4515</v>
       </c>
       <c r="E13" t="n">
-        <v>7.332</v>
+        <v>7.6673</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.483</v>
+        <v>-2.2158</v>
       </c>
       <c r="G13" t="n">
         <v>4.8339</v>
@@ -1468,13 +1468,13 @@
         <v>0.87</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2247</v>
+        <v>-0.6222</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0274</v>
+        <v>-0.6922</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1972</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0.3698</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8558</v>
+        <v>4.3926</v>
       </c>
       <c r="E14" t="n">
-        <v>5.2412</v>
+        <v>5.0177</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3855</v>
+        <v>-0.6251</v>
       </c>
       <c r="G14" t="n">
         <v>3.414</v>
@@ -1546,13 +1546,13 @@
         <v>0.87</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3837</v>
+        <v>-0.8469</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4194</v>
+        <v>-0.6429</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9644</v>
+        <v>-0.204</v>
       </c>
       <c r="V14" t="n">
         <v>0.9554</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8339</v>
+        <v>4.2886</v>
       </c>
       <c r="E15" t="n">
-        <v>3.894</v>
+        <v>4.5646</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0602</v>
+        <v>-0.2759</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1282</v>
@@ -1624,13 +1624,13 @@
         <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6029</v>
+        <v>-0.1481</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.536</v>
+        <v>0.1346</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0669</v>
+        <v>-0.2827</v>
       </c>
       <c r="V15" t="n">
         <v>2.8249</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>R. ANDERSSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2094</v>
+        <v>1.1532</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1952</v>
+        <v>0.4649</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9858</v>
+        <v>0.6883</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5782</v>
+        <v>0.5289</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0036</v>
+        <v>0.6843</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.5818</v>
+        <v>-0.1554</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0428</v>
+        <v>0.2978</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7369</v>
+        <v>0.6022</v>
       </c>
       <c r="L16" t="n">
-        <v>0.306</v>
+        <v>-0.3044</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.6211</v>
+        <v>0.2311</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7333</v>
+        <v>0.082</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8878</v>
+        <v>0.149</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6525</v>
+        <v>0.6525</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1149</v>
+        <v>-0.0282</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0022</v>
+        <v>0.167</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1127</v>
+        <v>-0.1953</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. ANDERSSON</t>
+          <t>A. GRELA ROJAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.868</v>
+        <v>0.149</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2414</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6267</v>
+        <v>0.149</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5289</v>
+        <v>0.149</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6843</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1554</v>
+        <v>0.149</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2978</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6022</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3044</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2311</v>
+        <v>0.149</v>
       </c>
       <c r="N17" t="n">
-        <v>0.082</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0.149</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6525</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6525</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3134</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0565</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2569</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GRELA ROJAS</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.149</v>
+        <v>0.0199</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1.0776</v>
       </c>
       <c r="F18" t="n">
-        <v>0.149</v>
+        <v>-1.0577</v>
       </c>
       <c r="G18" t="n">
-        <v>0.149</v>
+        <v>-0.5782</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1.0036</v>
       </c>
       <c r="I18" t="n">
-        <v>0.149</v>
+        <v>-1.5818</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2.0428</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1.7369</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.306</v>
       </c>
       <c r="M18" t="n">
-        <v>0.149</v>
+        <v>-2.6211</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.7333</v>
       </c>
       <c r="O18" t="n">
-        <v>0.149</v>
+        <v>-1.8878</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0.0745</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.1153</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.0408</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. KRAVIC</t>
+          <t>Y. BARRUETA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2604</v>
+        <v>-0.2726</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3897</v>
+        <v>1.0659</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1292</v>
+        <v>-1.3385</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5726</v>
+        <v>-0.9355</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9487</v>
+        <v>0.5929</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6239</v>
+        <v>-1.5284</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6042999999999999</v>
+        <v>1.6856</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6808</v>
+        <v>0.8791</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0765</v>
+        <v>0.8065</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9683</v>
+        <v>-2.6211</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2679</v>
+        <v>-0.2863</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7004</v>
+        <v>-2.3348</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7896</v>
+        <v>-0.7069</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9542</v>
+        <v>-0.6621</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1645</v>
+        <v>-0.0448</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.9347</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7395</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1745</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. DE SOUSA ANJO BRITO</t>
+          <t>D. KRAVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5523</v>
+        <v>-0.9001</v>
       </c>
       <c r="E20" t="n">
-        <v>2.4124</v>
+        <v>-1.0602</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9646</v>
+        <v>0.1601</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.368</v>
+        <v>-1.5726</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1405</v>
+        <v>-0.9487</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.5085</v>
+        <v>-0.6239</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2307</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9558</v>
+        <v>-0.6808</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7251</v>
+        <v>0.0765</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.5987</v>
+        <v>-0.9683</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8153</v>
+        <v>-0.2679</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7834</v>
+        <v>-0.7004</v>
       </c>
       <c r="P20" t="n">
         <v>1.0875</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1751</v>
+        <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0534</v>
+        <v>0.1499</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1392</v>
+        <v>0.2836</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0858</v>
+        <v>-0.1337</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.3252</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>-0.7395</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4552</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Y. BARRUETA</t>
+          <t>D. DE SOUSA ANJO BRITO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1603</v>
+        <v>-1.5696</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5071</v>
+        <v>1.5183</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6674</v>
+        <v>-3.0879</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9355</v>
+        <v>-1.368</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5929</v>
+        <v>1.1405</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5284</v>
+        <v>-2.5085</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6856</v>
+        <v>1.2307</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8791</v>
+        <v>1.9558</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8065</v>
+        <v>-0.7251</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6211</v>
+        <v>-2.5987</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2863</v>
+        <v>-0.8153</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.3348</v>
+        <v>-1.7834</v>
       </c>
       <c r="P21" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5225</v>
+        <v>2.1751</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5945</v>
+        <v>0.0361</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2209</v>
+        <v>0.2452</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3736</v>
+        <v>-0.2091</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9347</v>
+        <v>-1.3252</v>
       </c>
       <c r="W21" t="n">
         <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1952</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="22">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.8537</v>
+        <v>-4.8313</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.861</v>
+        <v>-2.414</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9927</v>
+        <v>-2.4173</v>
       </c>
       <c r="G23" t="n">
         <v>-3.0881</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4181</v>
+        <v>-0.3957</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8904</v>
+        <v>-0.4434</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5276999999999999</v>
+        <v>0.0478</v>
       </c>
       <c r="V23" t="n">
         <v>-1.13</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.1355</v>
+        <v>-5.5883</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.6525</v>
+        <v>-4.982</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.483</v>
+        <v>-0.6063</v>
       </c>
       <c r="G24" t="n">
         <v>-3.7293</v>
@@ -2326,13 +2326,13 @@
         <v>1.7401</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8837</v>
+        <v>-0.3365</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8099</v>
+        <v>-0.1394</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0738</v>
+        <v>-0.1971</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.014699999999999</v>
+        <v>0.4752000000000018</v>
       </c>
       <c r="E25" t="n">
         <v>12.6644</v>
       </c>
       <c r="F25" t="n">
-        <v>-13.6792</v>
+        <v>-12.189</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.589800000000001</v>
+        <v>-2.5898</v>
       </c>
       <c r="H25" t="n">
         <v>3.8927</v>
@@ -2380,10 +2380,10 @@
         <v>15.357</v>
       </c>
       <c r="K25" t="n">
-        <v>8.898399999999999</v>
+        <v>8.898400000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>6.4588</v>
+        <v>6.458800000000002</v>
       </c>
       <c r="M25" t="n">
         <v>-17.9469</v>
@@ -2404,13 +2404,13 @@
         <v>13.0503</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.0351</v>
+        <v>-3.545</v>
       </c>
       <c r="T25" t="n">
         <v>-2.1389</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.8961</v>
+        <v>-1.4061</v>
       </c>
       <c r="V25" t="n">
         <v>2.259800000000001</v>
